--- a/data/trans_camb/IP21-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP21-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,66; -0,74</t>
+          <t>-8,32; -0,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 1,54</t>
+          <t>-7,21; 1,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 0,17</t>
+          <t>-7,99; 0,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 2,34</t>
+          <t>-6,05; 2,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 1,43</t>
+          <t>-6,65; 1,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 1,14</t>
+          <t>-6,37; 1,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,75; -0,39</t>
+          <t>-5,94; -0,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 0,16</t>
+          <t>-5,36; -0,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,85; -0,35</t>
+          <t>-5,53; -0,2</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 35,86</t>
+          <t>-100,0; 43,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-93,06; 90,11</t>
+          <t>-100,0; 107,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-95,26; 31,41</t>
+          <t>-93,16; 56,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 182,79</t>
+          <t>-100,0; 252,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-91,17; 162,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-93,45; 116,17</t>
+          <t>-91,9; 127,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-88,0; 14,84</t>
+          <t>-89,15; 0,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-86,49; 19,38</t>
+          <t>-85,34; 6,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-85,84; -2,72</t>
+          <t>-85,61; 6,12</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 0,64</t>
+          <t>-9,01; 0,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 1,66</t>
+          <t>-8,38; 1,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 1,17</t>
+          <t>-8,28; 1,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 3,35</t>
+          <t>-4,85; 3,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 4,03</t>
+          <t>-4,45; 4,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,38; -0,16</t>
+          <t>-7,38; 0,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 1,18</t>
+          <t>-5,23; 0,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 1,6</t>
+          <t>-4,3; 1,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,39; -0,14</t>
+          <t>-6,28; -0,3</t>
         </is>
       </c>
     </row>
@@ -999,27 +999,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-94,21; 74,88</t>
+          <t>-100,0; 61,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-85,62; 125,66</t>
+          <t>-89,53; 51,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-90,61; 69,26</t>
+          <t>-90,36; 98,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 273,29</t>
+          <t>-89,48; 375,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-82,71; 320,35</t>
+          <t>-77,75; 459,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-80,25; 55,15</t>
+          <t>-81,15; 45,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-69,73; 71,81</t>
+          <t>-66,25; 71,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-88,3; 22,28</t>
+          <t>-90,95; 0,45</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 5,42</t>
+          <t>-1,87; 4,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 6,15</t>
+          <t>-0,97; 5,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 4,44</t>
+          <t>-1,9; 4,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 4,52</t>
+          <t>-6,16; 4,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 5,67</t>
+          <t>-5,51; 6,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,68; -0,79</t>
+          <t>-9,15; -0,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 3,09</t>
+          <t>-3,56; 2,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 4,02</t>
+          <t>-3,0; 4,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 0,28</t>
+          <t>-5,26; 0,14</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-75,23; 148,09</t>
+          <t>-76,39; 148,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-75,2; 206,83</t>
+          <t>-73,14; 215,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 110,42</t>
+          <t>-100,0; 87,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-66,0; 150,45</t>
+          <t>-68,2; 137,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-61,5; 211,04</t>
+          <t>-59,7; 217,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 63,56</t>
+          <t>-100,0; 32,69</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 7,31</t>
+          <t>0,14; 7,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 0,9</t>
+          <t>-4,58; 0,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,73; -0,79</t>
+          <t>-5,43; -0,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 3,22</t>
+          <t>-3,55; 3,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,24; -0,14</t>
+          <t>-6,26; -0,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 0,07</t>
+          <t>-5,85; 0,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 4,39</t>
+          <t>-0,97; 3,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,26; -0,24</t>
+          <t>-4,38; -0,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,88; -0,92</t>
+          <t>-4,73; -0,93</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 340,94</t>
+          <t>-1,32; 344,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-83,24; 52,19</t>
+          <t>-83,92; 68,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-95,83; -14,6</t>
+          <t>-95,56; -14,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-54,49; 106,59</t>
+          <t>-53,13; 116,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-87,56; 8,42</t>
+          <t>-86,46; 9,98</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-87,91; 23,38</t>
+          <t>-85,61; 33,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-17,26; 146,07</t>
+          <t>-18,58; 135,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-77,36; -4,27</t>
+          <t>-79,21; -11,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-86,35; -20,21</t>
+          <t>-83,79; -11,69</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 3,69</t>
+          <t>-3,2; 3,49</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 4,7</t>
+          <t>-2,79; 4,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 2,0</t>
+          <t>-4,52; 1,92</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 5,12</t>
+          <t>-3,16; 5,3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 4,28</t>
+          <t>-3,41; 4,44</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 1,09</t>
+          <t>-5,71; 0,83</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 3,14</t>
+          <t>-1,93; 3,15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 3,46</t>
+          <t>-1,86; 3,49</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 0,54</t>
+          <t>-3,97; 0,57</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-70,42; 346,13</t>
+          <t>-71,15; 330,5</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-57,24; 459,75</t>
+          <t>-60,34; 422,86</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 230,94</t>
+          <t>-100,0; 224,89</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-58,47; 259,59</t>
+          <t>-59,85; 257,64</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-66,97; 224,22</t>
+          <t>-64,72; 229,09</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-89,98; 110,87</t>
+          <t>-89,69; 74,04</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-54,66; 147,51</t>
+          <t>-43,73; 158,38</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-43,65; 174,31</t>
+          <t>-42,62; 170,07</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-81,74; 37,16</t>
+          <t>-80,12; 37,0</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 5,13</t>
+          <t>-3,78; 5,59</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 7,25</t>
+          <t>-2,62; 7,67</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,09; -0,82</t>
+          <t>-7,08; -0,83</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 7,26</t>
+          <t>-5,53; 7,27</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,25; -0,7</t>
+          <t>-10,49; -0,93</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 0,67</t>
+          <t>-10,07; -0,09</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 4,72</t>
+          <t>-3,04; 4,72</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 1,79</t>
+          <t>-5,21; 1,72</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,59; -0,97</t>
+          <t>-6,73; -0,95</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-68,06; 298,94</t>
+          <t>-69,71; 291,34</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 231,27</t>
+          <t>-100,0; 82,69</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 293,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-59,71; 212,84</t>
+          <t>-56,02; 216,41</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-83,61; 109,88</t>
+          <t>-85,53; 103,14</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 38,5</t>
+          <t>-100,0; -14,55</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 1,91</t>
+          <t>-1,44; 1,74</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 0,59</t>
+          <t>-2,35; 0,68</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,7; -0,95</t>
+          <t>-3,74; -1,08</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,65</t>
+          <t>-1,97; 1,48</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 0,15</t>
+          <t>-3,28; -0,02</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,46; -1,41</t>
+          <t>-4,48; -1,49</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 1,13</t>
+          <t>-1,3; 1,18</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,46; -0,17</t>
+          <t>-2,38; -0,09</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,68; -1,58</t>
+          <t>-3,64; -1,64</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-34,61; 67,52</t>
+          <t>-33,87; 60,57</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-53,85; 21,13</t>
+          <t>-52,6; 24,95</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-79,35; -27,64</t>
+          <t>-80,24; -33,27</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-35,12; 44,92</t>
+          <t>-37,61; 39,51</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-59,36; 3,93</t>
+          <t>-59,51; -0,29</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-79,32; -35,52</t>
+          <t>-80,75; -37,36</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-26,98; 32,88</t>
+          <t>-27,06; 33,69</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-51,73; -4,24</t>
+          <t>-49,34; -1,92</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-75,56; -42,66</t>
+          <t>-76,04; -45,74</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP21-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP21-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,32; -0,34</t>
+          <t>-8,72; -0,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 1,6</t>
+          <t>-7,3; 1,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 0,43</t>
+          <t>-8,2; 0,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 2,31</t>
+          <t>-6,07; 2,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 1,13</t>
+          <t>-6,7; 0,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 1,06</t>
+          <t>-6,09; 1,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,94; -0,35</t>
+          <t>-5,62; -0,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,36; -0,0</t>
+          <t>-5,76; 0,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,53; -0,2</t>
+          <t>-5,9; -0,61</t>
         </is>
       </c>
     </row>
@@ -783,22 +783,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 43,16</t>
+          <t>-100,0; 29,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 107,93</t>
+          <t>-92,16; 76,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-93,16; 56,08</t>
+          <t>-100,0; 44,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 252,04</t>
+          <t>-100,0; 197,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -808,22 +808,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-91,9; 127,68</t>
+          <t>-91,19; 90,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-89,15; 0,01</t>
+          <t>-89,35; -0,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-85,34; 6,36</t>
+          <t>-86,6; 26,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-85,61; 6,12</t>
+          <t>-87,84; -1,55</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 0,33</t>
+          <t>-8,42; 0,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 1,28</t>
+          <t>-8,07; 1,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 1,45</t>
+          <t>-8,31; 1,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 3,62</t>
+          <t>-5,05; 3,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 4,57</t>
+          <t>-3,9; 4,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 0,0</t>
+          <t>-6,95; -0,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 0,96</t>
+          <t>-5,12; 1,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 1,9</t>
+          <t>-4,56; 1,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,28; -0,3</t>
+          <t>-5,93; -0,16</t>
         </is>
       </c>
     </row>
@@ -999,27 +999,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 61,97</t>
+          <t>-100,0; 75,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-89,53; 51,5</t>
+          <t>-87,19; 91,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-90,36; 98,84</t>
+          <t>-89,73; 83,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-89,48; 375,78</t>
+          <t>-88,87; 360,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-77,75; 459,76</t>
+          <t>-75,77; 420,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-81,15; 45,96</t>
+          <t>-81,06; 60,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,25; 71,18</t>
+          <t>-71,28; 81,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-90,95; 0,45</t>
+          <t>-89,8; 9,44</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 4,56</t>
+          <t>-1,85; 5,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 5,98</t>
+          <t>-1,79; 5,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 4,1</t>
+          <t>-2,01; 3,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 4,13</t>
+          <t>-5,8; 4,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 6,3</t>
+          <t>-5,04; 6,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,15; -0,64</t>
+          <t>-9,06; -0,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 2,89</t>
+          <t>-3,52; 2,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 4,23</t>
+          <t>-2,9; 4,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 0,14</t>
+          <t>-5,66; -0,07</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-76,39; 148,95</t>
+          <t>-73,85; 184,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-73,14; 215,95</t>
+          <t>-69,45; 281,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 87,07</t>
+          <t>-100,0; 45,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-68,2; 137,61</t>
+          <t>-70,54; 148,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-59,7; 217,92</t>
+          <t>-59,66; 201,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 32,69</t>
+          <t>-100,0; 51,03</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 7,2</t>
+          <t>0,24; 7,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 0,89</t>
+          <t>-4,01; 1,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,43; -0,67</t>
+          <t>-5,28; -0,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 3,42</t>
+          <t>-3,75; 3,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,26; -0,18</t>
+          <t>-5,89; 0,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 0,32</t>
+          <t>-5,97; 0,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 3,81</t>
+          <t>-0,92; 3,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,38; -0,47</t>
+          <t>-4,45; -0,3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,73; -0,93</t>
+          <t>-4,93; -0,69</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 344,81</t>
+          <t>-0,04; 322,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-83,92; 68,59</t>
+          <t>-82,45; 79,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-95,56; -14,41</t>
+          <t>-96,05; -10,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-53,13; 116,81</t>
+          <t>-56,2; 91,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-86,46; 9,98</t>
+          <t>-86,29; 16,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-85,61; 33,4</t>
+          <t>-85,49; 30,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-18,58; 135,45</t>
+          <t>-19,3; 124,3</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-79,21; -11,23</t>
+          <t>-77,46; 1,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-83,79; -11,69</t>
+          <t>-85,56; -12,75</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 3,49</t>
+          <t>-3,75; 3,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 4,66</t>
+          <t>-2,62; 5,28</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 1,92</t>
+          <t>-4,65; 2,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 5,3</t>
+          <t>-2,59; 5,99</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 4,44</t>
+          <t>-3,63; 4,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 0,83</t>
+          <t>-5,38; 1,41</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 3,15</t>
+          <t>-2,24; 3,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 3,49</t>
+          <t>-2,07; 3,25</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 0,57</t>
+          <t>-3,94; 0,51</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-71,15; 330,5</t>
+          <t>-72,07; 344,0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-60,34; 422,86</t>
+          <t>-58,08; 457,48</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 224,89</t>
+          <t>-100,0; 181,69</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-59,85; 257,64</t>
+          <t>-51,48; 334,06</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-64,72; 229,09</t>
+          <t>-69,4; 207,27</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-89,69; 74,04</t>
+          <t>-87,75; 118,69</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-43,73; 158,38</t>
+          <t>-45,4; 158,79</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-42,62; 170,07</t>
+          <t>-44,14; 157,43</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-80,12; 37,0</t>
+          <t>-79,39; 33,04</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 5,59</t>
+          <t>-4,08; 5,19</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 7,67</t>
+          <t>-2,99; 6,64</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,08; -0,83</t>
+          <t>-7,1; -0,81</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 7,27</t>
+          <t>-5,41; 7,13</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,49; -0,93</t>
+          <t>-10,25; -0,9</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-10,07; -0,09</t>
+          <t>-9,78; -0,36</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 4,72</t>
+          <t>-2,91; 4,99</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 1,72</t>
+          <t>-4,91; 1,29</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,73; -0,95</t>
+          <t>-6,46; -0,93</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-69,71; 291,34</t>
+          <t>-68,68; 276,54</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 82,69</t>
+          <t>-100,0; 111,66</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 188,1</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>-55,44; 211,53</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>-87,06; 67,16</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-56,02; 216,41</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-85,53; 103,14</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; -14,55</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 1,74</t>
+          <t>-1,38; 1,86</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 0,68</t>
+          <t>-2,36; 0,68</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,74; -1,08</t>
+          <t>-3,79; -1,02</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,48</t>
+          <t>-1,83; 1,72</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,28; -0,02</t>
+          <t>-3,22; 0,13</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,48; -1,49</t>
+          <t>-4,32; -1,41</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,18</t>
+          <t>-1,22; 1,17</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,38; -0,09</t>
+          <t>-2,34; -0,09</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,64; -1,64</t>
+          <t>-3,6; -1,53</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-33,87; 60,57</t>
+          <t>-31,42; 69,23</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-52,6; 24,95</t>
+          <t>-50,06; 24,51</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-80,24; -33,27</t>
+          <t>-80,06; -30,48</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-37,61; 39,51</t>
+          <t>-34,58; 48,56</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-59,51; -0,29</t>
+          <t>-59,29; 3,86</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-80,75; -37,36</t>
+          <t>-78,84; -36,23</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-27,06; 33,69</t>
+          <t>-26,12; 33,56</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-49,34; -1,92</t>
+          <t>-50,24; -2,81</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-76,04; -45,74</t>
+          <t>-75,2; -42,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP21-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP21-Clase-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses</t>
+          <t>Menores que han estado ingresados/as en un hospital en los últimos 12 meses</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-1,86</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-2,24</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-2,34</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-3,99</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-2,94</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-3,51</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,86</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-2,24</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,19</t>
+          <t>-3,46</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,86</t>
+          <t>-2,92</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,72; -0,7</t>
+          <t>-5,48; 2,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 1,28</t>
+          <t>-6,31; 1,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 0,31</t>
+          <t>-6,6; 0,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 2,24</t>
+          <t>-8,66; -0,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 0,98</t>
+          <t>-7,76; 1,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 1,13</t>
+          <t>-8,38; 0,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,62; -0,32</t>
+          <t>-5,75; -0,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 0,06</t>
+          <t>-5,62; 0,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,9; -0,61</t>
+          <t>-5,77; -0,46</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-45,68%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-54,95%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-57,42%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-75,69%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-55,69%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-66,55%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-45,68%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-54,95%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-53,69%</t>
+          <t>-65,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-60,94%</t>
+          <t>-62,31%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 29,9</t>
+          <t>-100,0; 182,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-92,16; 76,91</t>
+          <t>-91,17; 162,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 44,25</t>
+          <t>-93,8; 100,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 197,35</t>
+          <t>-100,0; 35,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-93,06; 90,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-91,19; 90,97</t>
+          <t>-95,67; 37,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-89,35; -0,43</t>
+          <t>-88,0; 14,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-86,6; 26,6</t>
+          <t>-86,49; 19,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-87,84; -1,55</t>
+          <t>-86,18; -3,74</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,39</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-2,67</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-3,81</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-2,97</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-3,22</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,39</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,24</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-2,7</t>
+          <t>-3,38</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,97</t>
+          <t>-3,01</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 0,81</t>
+          <t>-5,65; 3,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 1,38</t>
+          <t>-4,76; 4,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 1,25</t>
+          <t>-7,35; -0,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 3,71</t>
+          <t>-9,35; 0,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 4,46</t>
+          <t>-7,9; 1,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,95; -0,17</t>
+          <t>-8,99; 0,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 1,16</t>
+          <t>-5,36; 1,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 1,77</t>
+          <t>-4,9; 1,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,93; -0,16</t>
+          <t>-6,45; -0,21</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-11,5%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7,2%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-79,6%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-64,28%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-50,06%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-54,2%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-11,5%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,2%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-80,37%</t>
+          <t>-56,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-63,84%</t>
+          <t>-64,64%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 75,93</t>
+          <t>-100,0; 273,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-87,19; 91,31</t>
+          <t>-82,71; 320,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-89,73; 83,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-88,87; 360,87</t>
+          <t>-94,21; 74,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-75,77; 420,51</t>
+          <t>-85,62; 125,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-91,26; 65,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-81,06; 60,33</t>
+          <t>-80,25; 55,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-71,28; 81,96</t>
+          <t>-69,73; 71,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-89,8; 9,44</t>
+          <t>-88,98; 21,86</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,85</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,19</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-4,66</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>1,44</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1,84</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,73</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,85</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,19</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-4,57</t>
+          <t>0,52</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,39</t>
+          <t>-2,52</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 5,39</t>
+          <t>-5,95; 4,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 5,92</t>
+          <t>-5,99; 5,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 3,9</t>
+          <t>-8,8; -0,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 4,88</t>
+          <t>-1,28; 5,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 6,74</t>
+          <t>-0,96; 6,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,06; -0,8</t>
+          <t>-1,88; 4,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 2,84</t>
+          <t>-3,53; 3,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 4,26</t>
+          <t>-3,03; 4,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,66; -0,07</t>
+          <t>-5,55; 0,06</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-15,43%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-3,42%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-84,12%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>154,59%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>197,96%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>78,47%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-15,43%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-3,42%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-82,45%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-65,15%</t>
+          <t>-68,53%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>-75,23; 148,09</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>-75,2; 206,83</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 82,14</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-73,85; 184,08</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-69,45; 281,93</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 45,07</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-70,54; 148,83</t>
+          <t>-66,0; 150,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-59,66; 201,78</t>
+          <t>-61,5; 211,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 51,03</t>
+          <t>-100,0; 55,45</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-2,88</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-2,65</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>3,5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-1,62</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-2,77</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,17</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-2,88</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,76</t>
+          <t>-2,7</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,76</t>
+          <t>-2,63</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 7,46</t>
+          <t>-3,54; 3,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 1,01</t>
+          <t>-6,24; -0,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,28; -0,82</t>
+          <t>-6,01; 0,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 3,12</t>
+          <t>0,24; 7,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 0,14</t>
+          <t>-4,2; 0,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 0,31</t>
+          <t>-5,69; -0,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 3,94</t>
+          <t>-0,85; 4,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,45; -0,3</t>
+          <t>-4,26; -0,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,93; -0,69</t>
+          <t>-4,78; -0,64</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-3,5%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-58,13%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-53,57%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>98,57%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-45,6%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-77,91%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-3,5%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-58,13%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-55,67%</t>
+          <t>-75,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-64,96%</t>
+          <t>-61,86%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 322,24</t>
+          <t>-54,49; 106,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-82,45; 79,25</t>
+          <t>-87,56; 8,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-96,05; -10,84</t>
+          <t>-86,85; 36,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-56,2; 91,44</t>
+          <t>-1,75; 340,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-86,29; 16,17</t>
+          <t>-83,24; 52,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-85,49; 30,16</t>
+          <t>-94,73; -0,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,3; 124,3</t>
+          <t>-17,26; 146,07</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-77,46; 1,51</t>
+          <t>-77,36; -4,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-85,56; -12,75</t>
+          <t>-85,54; -11,77</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,16</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,3</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-2,03</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,21</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1,13</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-1,14</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,16</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,3</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,9</t>
+          <t>-1,16</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,56</t>
+          <t>-1,64</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 3,53</t>
+          <t>-2,94; 5,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 5,28</t>
+          <t>-3,51; 4,28</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 2,1</t>
+          <t>-5,24; 0,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 5,99</t>
+          <t>-3,52; 3,69</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 4,19</t>
+          <t>-2,6; 4,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 1,41</t>
+          <t>-4,67; 2,01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 3,35</t>
+          <t>-2,62; 3,14</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 3,25</t>
+          <t>-2,1; 3,46</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 0,51</t>
+          <t>-4,29; 0,43</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>31,05%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>7,95%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-54,19%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>7,03%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>37,58%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-37,98%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>31,05%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>7,95%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-50,75%</t>
+          <t>-38,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-45,7%</t>
+          <t>-47,99%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-72,07; 344,0</t>
+          <t>-58,47; 259,59</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-58,08; 457,48</t>
+          <t>-66,97; 224,22</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 181,69</t>
+          <t>-89,97; 97,9</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-51,48; 334,06</t>
+          <t>-70,42; 346,13</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-69,4; 207,27</t>
+          <t>-57,24; 459,75</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-87,75; 118,69</t>
+          <t>-100,0; 231,52</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-45,4; 158,79</t>
+          <t>-54,66; 147,51</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-44,14; 157,43</t>
+          <t>-43,65; 174,31</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-79,39; 33,04</t>
+          <t>-82,61; 34,87</t>
         </is>
       </c>
     </row>
@@ -1704,34 +1704,34 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>0,72</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-4,7</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-4,32</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-0,08</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1,43</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>-2,64</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>0,72</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-4,7</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-4,46</t>
-        </is>
-      </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
           <t>0,63</t>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-3,51</t>
+          <t>-3,47</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 5,19</t>
+          <t>-5,47; 7,26</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 6,64</t>
+          <t>-10,25; -0,7</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,1; -0,81</t>
+          <t>-9,33; 1,1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 7,13</t>
+          <t>-4,35; 5,13</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,25; -0,9</t>
+          <t>-2,75; 7,25</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,78; -0,36</t>
+          <t>-7,09; -0,82</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 4,99</t>
+          <t>-3,44; 4,72</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 1,29</t>
+          <t>-5,24; 1,79</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,46; -0,93</t>
+          <t>-6,58; -0,82</t>
         </is>
       </c>
     </row>
@@ -1810,34 +1810,34 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>12,72%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-83,41%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-76,77%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-3,13%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>54,01%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>12,72%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-83,41%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-79,14%</t>
-        </is>
-      </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
           <t>15,38%</t>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-85,4%</t>
+          <t>-84,32%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>-68,06; 298,94</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 231,27</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 350,26</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>-68,68; 276,54</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 111,66</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 188,1</t>
-        </is>
-      </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-55,44; 211,53</t>
+          <t>-59,71; 212,84</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-87,06; 67,16</t>
+          <t>-83,61; 109,88</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 49,98</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,17</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-1,64</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-2,91</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>0,13</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-0,82</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-2,28</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,17</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-1,64</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-2,89</t>
+          <t>-2,26</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,86</t>
+          <t>-1,85; 1,65</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 0,68</t>
+          <t>-3,21; 0,15</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,79; -1,02</t>
+          <t>-4,47; -1,39</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,72</t>
+          <t>-1,59; 1,91</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 0,13</t>
+          <t>-2,56; 0,59</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,32; -1,41</t>
+          <t>-3,66; -0,9</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,17</t>
+          <t>-1,25; 1,13</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,34; -0,09</t>
+          <t>-2,46; -0,17</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,6; -1,53</t>
+          <t>-3,67; -1,57</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-3,7%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-36,0%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-63,95%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>3,51%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-22,28%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-61,96%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-3,7%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-36,0%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-63,5%</t>
+          <t>-61,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-62,74%</t>
+          <t>-62,8%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-31,42; 69,23</t>
+          <t>-35,12; 44,92</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-50,06; 24,51</t>
+          <t>-59,36; 3,93</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-80,06; -30,48</t>
+          <t>-79,71; -34,82</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-34,58; 48,56</t>
+          <t>-34,61; 67,52</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-59,29; 3,86</t>
+          <t>-53,85; 21,13</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-78,84; -36,23</t>
+          <t>-79,07; -27,38</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-26,12; 33,56</t>
+          <t>-26,98; 32,88</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-50,24; -2,81</t>
+          <t>-51,73; -4,24</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-75,2; -42,78</t>
+          <t>-75,52; -43,22</t>
         </is>
       </c>
     </row>
